--- a/presupuesto.xlsx
+++ b/presupuesto.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3328BA7-10D8-4FA1-B88B-B66F14791C8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBFCEF66-9A80-4B04-A922-BDE4515E9A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{981E974B-7273-4E8D-BDFA-2918E0C41C8B}"/>
   </bookViews>
@@ -28,7 +28,7 @@
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -58,46 +58,46 @@
     <t>Total</t>
   </si>
   <si>
+    <t>PRESUPUESTO</t>
+  </si>
+  <si>
     <t>Y.R</t>
   </si>
   <si>
-    <t>Tarifa/h</t>
-  </si>
-  <si>
-    <t>Descripción</t>
+    <t>351-325-8772</t>
+  </si>
+  <si>
+    <t>Yagosamir28@gmail.com</t>
+  </si>
+  <si>
+    <t>Alias</t>
+  </si>
+  <si>
+    <t>Yroberti.nx</t>
+  </si>
+  <si>
+    <t>Presupuesto a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha final </t>
+  </si>
+  <si>
+    <t>Fecha de inicio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descripción </t>
   </si>
   <si>
     <t>Horas</t>
   </si>
   <si>
-    <t>351-325-8772</t>
-  </si>
-  <si>
-    <t>Yagosamir28@gmail.com</t>
-  </si>
-  <si>
-    <t>PRESUPUESTO</t>
-  </si>
-  <si>
-    <t>Alias:</t>
-  </si>
-  <si>
-    <t>Yroberti.nx</t>
-  </si>
-  <si>
-    <t>Presupuesto a</t>
-  </si>
-  <si>
-    <t>Fecha de inicio</t>
-  </si>
-  <si>
-    <t>Fecha final</t>
+    <t xml:space="preserve">Tarifa/h </t>
   </si>
   <si>
     <t>Válido por 7 días corridos</t>
   </si>
   <si>
-    <t>Margen de imprevistos</t>
+    <t xml:space="preserve">Margen de imprevistos </t>
   </si>
 </sst>
 </file>
@@ -107,7 +107,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +174,14 @@
       <name val="Malgun Gothic"/>
       <family val="2"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Malgun Gothic"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -251,18 +259,19 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="3"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="medium">
+        <color theme="8" tint="-0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -282,12 +291,18 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
@@ -298,6 +313,9 @@
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -320,12 +338,21 @@
     <xf numFmtId="10" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -335,25 +362,13 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -501,13 +516,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="medium">
-          <color theme="4" tint="-0.499984740745262"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -521,6 +529,13 @@
         <scheme val="minor"/>
       </font>
       <alignment vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="medium">
+          <color theme="4" tint="-0.499984740745262"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -543,6 +558,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleLight1" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF156082"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -555,7 +575,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5364632-DD8B-4ACD-AF42-DD7435917C23}" name="InvoiceDetails" displayName="InvoiceDetails" ref="C16:G24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C5364632-DD8B-4ACD-AF42-DD7435917C23}" name="InvoiceDetails" displayName="InvoiceDetails" ref="C16:G24" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
   <autoFilter ref="C16:G24" xr:uid="{C5364632-DD8B-4ACD-AF42-DD7435917C23}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -565,11 +585,11 @@
   </autoFilter>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{3CD4573A-0F86-401E-9173-167482BBB9AD}" name="Item" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{541C06C2-0318-4F4E-8923-4F9A6C26A24A}" name="Descripción" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{541C06C2-0318-4F4E-8923-4F9A6C26A24A}" name="Descripción " dataDxfId="3"/>
     <tableColumn id="5" xr3:uid="{A430CA4B-FF4F-453F-A45E-1323E6E982F3}" name="Horas" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{754EC82C-98F0-49A7-8BCD-74E397EEAF35}" name="Tarifa/h" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{754EC82C-98F0-49A7-8BCD-74E397EEAF35}" name="Tarifa/h " dataDxfId="1"/>
     <tableColumn id="7" xr3:uid="{A9538594-E8D6-4FDD-A0F1-A5AAFA967C31}" name="Total" dataDxfId="0">
-      <calculatedColumnFormula>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</calculatedColumnFormula>
+      <calculatedColumnFormula>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -807,7 +827,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2.625" customWidth="1"/>
-    <col min="3" max="3" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.625" customWidth="1"/>
     <col min="5" max="7" width="14.625" customWidth="1"/>
     <col min="8" max="9" width="2.625" customWidth="1"/>
@@ -824,58 +844,58 @@
     </row>
     <row r="2" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1"/>
-      <c r="C2" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="25"/>
+      <c r="C2" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="31"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="25"/>
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
-      <c r="G4" s="8" t="s">
-        <v>12</v>
+      <c r="G4" s="34" t="s">
+        <v>10</v>
       </c>
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="G5" s="8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H6" s="1"/>
     </row>
@@ -889,299 +909,299 @@
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
     </row>
     <row r="9" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="16" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="18"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="18"/>
+      <c r="C11" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18"/>
+      <c r="C12" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="2:8" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="18"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="18"/>
+      <c r="C16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="15"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="15"/>
-      <c r="C11" s="23" t="s">
+      <c r="E16" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="18" t="s">
+      <c r="F16" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="18"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="18"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="18"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="18"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H20" s="18"/>
+    </row>
+    <row r="21" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="18"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H21" s="18"/>
+    </row>
+    <row r="22" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="18"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H22" s="18"/>
+    </row>
+    <row r="23" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="18"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H23" s="18"/>
+    </row>
+    <row r="24" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="18"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16" t="str">
+        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h ]],"")))</f>
+        <v/>
+      </c>
+      <c r="H24" s="18"/>
+    </row>
+    <row r="25" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="27" t="str">
+        <f>IFERROR(#REF!*G27,"0")</f>
         <v>0</v>
       </c>
-      <c r="H11" s="15"/>
-    </row>
-    <row r="12" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="15"/>
-      <c r="C12" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="15"/>
-    </row>
-    <row r="13" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-    </row>
-    <row r="15" spans="2:8" ht="15.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="15"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="15"/>
-    </row>
-    <row r="16" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="15"/>
-      <c r="C16" s="28" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="G16" s="28" t="s">
+      <c r="H25" s="18"/>
+    </row>
+    <row r="26" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="18"/>
+      <c r="C26" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="30"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="H16" s="15"/>
-    </row>
-    <row r="17" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="15"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="18" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="15"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H18" s="15"/>
-    </row>
-    <row r="19" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="15"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H19" s="15"/>
-    </row>
-    <row r="20" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="15"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H20" s="15"/>
-    </row>
-    <row r="21" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="15"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H21" s="15"/>
-    </row>
-    <row r="22" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="15"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H22" s="15"/>
-    </row>
-    <row r="23" spans="2:8" ht="26.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="15"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H23" s="15"/>
-    </row>
-    <row r="24" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="15"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14" t="str">
-        <f>IF(ISBLANK(InvoiceDetails[[#This Row],[Horas]]),"",(IFERROR(InvoiceDetails[[#This Row],[Horas]]*InvoiceDetails[[#This Row],[Tarifa/h]],"")))</f>
-        <v/>
-      </c>
-      <c r="H24" s="15"/>
-    </row>
-    <row r="25" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G25" s="22">
-        <v>0.05</v>
-      </c>
-      <c r="H25" s="15"/>
-    </row>
-    <row r="26" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="15"/>
-      <c r="C26" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="33" t="s">
-        <v>6</v>
-      </c>
-      <c r="G26" s="34" t="e">
-        <f>#REF!-#REF!+G28</f>
+      <c r="G26" s="17" t="e">
+        <f>#REF!-#REF!+G25</f>
         <v>#REF!</v>
       </c>
-      <c r="H26" s="15"/>
+      <c r="H26" s="18"/>
     </row>
     <row r="27" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="15"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="15"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="18"/>
     </row>
     <row r="28" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="15"/>
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="18"/>
     </row>
     <row r="29" spans="2:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="31"/>
-      <c r="G29" s="31"/>
-      <c r="H29" s="15"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="18"/>
     </row>
     <row r="30" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
     </row>
     <row r="31" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
     </row>
     <row r="32" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
     </row>
     <row r="33" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
     </row>
     <row r="34" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1"/>
@@ -1193,13 +1213,13 @@
       <c r="H34" s="1"/>
     </row>
     <row r="35" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
     </row>
     <row r="36" spans="2:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="1"/>
@@ -1217,7 +1237,7 @@
     <mergeCell ref="C2:D6"/>
     <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="6">
+  <dataValidations count="6">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Create a Timesheet invoice in this worksheet. Helpful instructions on how to use this worksheet are in cells in this column. Arrow down to get started." sqref="A1" xr:uid="{8C706B6D-8096-4942-B39B-CE946CFA40F3}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Company Name, Company Street Address, City, State, and ZIP/Postal Code, Phone and E-mail in cell G2 through G6" sqref="A2" xr:uid="{472DE285-FC61-41D3-9B10-E04A808C4529}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter BILL TO details such as Client Company Name, Address, Phone and Email in cells G10 through G13" sqref="A9" xr:uid="{4A2A9408-5113-42FD-81EB-EE3928FA3A58}"/>
@@ -1225,16 +1245,28 @@
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Invoice Number, Invoice Date and Due Date in cells D10 through D12" sqref="A10" xr:uid="{5A4A7D2B-9A23-4616-92F8-7782E0523C13}"/>
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Enter Invoice Terms and Conditions in cell C27" sqref="A26" xr:uid="{10517E83-13CC-426C-BE2E-03CAF4A833DD}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="G4" r:id="rId1" xr:uid="{34D8CF01-ADD5-4960-8654-A43198A6CBF7}"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="89" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="91" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001867FBBEFD40724CA20725D6B3094130" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b563ecc397a77cd5d82b22a852f9d63c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="21705155-b4ce-4c69-95dc-4fd6cb8c5571" xmlns:ns3="38de0ec0-4312-429b-9ba4-a6f7899b86f2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="514fef1a96c1431b584933149cb0dc9f" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -1452,7 +1484,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -1465,16 +1497,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27CDC99A-BC37-45F3-99C8-82408109060C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B40C2F4-6ABE-4EAB-96E4-B603338C2548}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1494,7 +1525,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{524C15C7-81D5-4EB8-8478-93675F4A8C50}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -1506,14 +1537,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27CDC99A-BC37-45F3-99C8-82408109060C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>